--- a/out/Village_map_of_Tiruvallur_Gummidipoondi_Manellore_13.455683_80.019989.xlsx
+++ b/out/Village_map_of_Tiruvallur_Gummidipoondi_Manellore_13.455683_80.019989.xlsx
@@ -1058,11 +1058,6 @@
           <t>146</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 2, 20, 21, 22, 23, 24, 25, 26, 27A, 27B, 28, 3, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1070,11 +1065,6 @@
           <t>147</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 2, 20, 21, 22, 23, 24, 3, 4, 5, 6, 7A, 7B, 7C, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1082,11 +1072,6 @@
           <t>148</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>1, 2A, 2B, 2C, 2D, 2E, 2F, 3A, 3B1, 3B2, 3C, 3D, 4A, 4B, 4C, 4D, 4E, 4F1, 4F2, 4F3, 4G, 4H, 5</t>
-        </is>
-      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1094,11 +1079,6 @@
           <t>149</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>1A, 1B, 1C, 2, 3, 4, 5A, 5B, 6</t>
-        </is>
-      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1106,11 +1086,6 @@
           <t>15</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>1, 10A, 10B, 11, 12, 13, 14, 15, 16, 17, 18, 19, 20, 21A, 21B, 22A, 22B, 22C, 22D, 22E, 22F, 22G, 22H, 23, 24, 25, 26, 27, 2A, 2B, 3A, 3B, 4, 5A, 5B, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1118,11 +1093,6 @@
           <t>150</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>1, 2, 3A1, 3A2, 3B1, 3B2, 3C1, 3C2, 3D, 3E1, 3E2, 3E3, 3F, 4, 5, 6, 7</t>
-        </is>
-      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1130,11 +1100,6 @@
           <t>151</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13, 14, 15, 16A, 16B, 17, 18, 19A, 19B, 20, 21, 2A, 2B, 3, 4, 5A, 5B1, 5B2, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1142,11 +1107,6 @@
           <t>152</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 2, 20, 21, 3, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1154,11 +1114,6 @@
           <t>153</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13A1, 13A2, 13B, 14, 2A, 2B, 3, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -1166,11 +1121,6 @@
           <t>154</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>1, 10, 11A, 11B1, 11B2, 12A, 12B1, 12B2, 13, 14A1, 14A2, 14B, 15A1, 15A2, 15B, 16A, 16B, 17A, 17B, 2, 3, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1178,11 +1128,6 @@
           <t>155</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>1, 10A1, 10A2, 10A3, 10B, 10C, 2, 3, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -1190,11 +1135,6 @@
           <t>156</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 2, 3, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -1202,11 +1142,6 @@
           <t>157</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 2, 20, 21A, 21B, 22, 23, 24, 25, 26, 27, 28, 29, 30, 3A, 3B, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -1214,11 +1149,6 @@
           <t>158</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13, 14A, 14B, 15, 16, 17, 18, 2, 3, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -1226,11 +1156,6 @@
           <t>159</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 2, 3, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -1238,11 +1163,6 @@
           <t>16</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12A, 12B, 13, 14, 15, 16, 17, 18, 19, 2, 20, 21, 22, 23, 24, 25, 3, 4, 5, 6, 7, 8A, 8B, 9</t>
-        </is>
-      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -1250,11 +1170,6 @@
           <t>160</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>10, 11, 12, 13, 14, 15, 16, 17, 1A, 1B, 2, 3, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -1262,11 +1177,6 @@
           <t>161</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>1, 2, 3, 4A, 4B, 5, 6, 7, 8</t>
-        </is>
-      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -1274,11 +1184,6 @@
           <t>162</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 2, 20, 21, 22, 23, 3A, 3B, 4A, 4B, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -1286,11 +1191,6 @@
           <t>163</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>10, 11, 12A, 12B, 12C, 12D, 1A, 1B, 2A, 2B1, 2B2, 3, 4, 5, 6, 7, 8A, 8B, 9</t>
-        </is>
-      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -1298,11 +1198,6 @@
           <t>164</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>1, 10, 2A1, 2A2, 2B, 3, 4, 5A, 5B, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -1310,11 +1205,6 @@
           <t>165</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13, 14, 15A1, 15A2, 15B, 15C1, 15C2, 16, 17, 18A, 18B1, 18B2, 2, 3, 4, 5, 6, 7A, 7B, 7C, 7D, 7E, 8, 9A, 9B</t>
-        </is>
-      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -1322,11 +1212,6 @@
           <t>166</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>1, 10, 11A, 11B, 12A, 12B, 13, 14, 15, 16A, 16B, 16C, 17, 18, 2, 3, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -1334,11 +1219,6 @@
           <t>167</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12A, 12B, 13A, 13B, 14, 15, 16, 17, 18, 2, 3A1, 3A2, 3B, 3C, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -1346,11 +1226,6 @@
           <t>168</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>1, 10A, 10B, 11A, 11B, 12, 13, 14, 15, 16, 2, 3, 4, 5, 6A, 6B, 7, 8, 9A, 9B, 9C, 9D, 9E, 9F</t>
-        </is>
-      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -1358,11 +1233,6 @@
           <t>169</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 1A, 1B, 1C, 1D, 2, 20, 3, 4, 5, 6, 7, 8A, 8B, 9</t>
-        </is>
-      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -1370,11 +1240,6 @@
           <t>17</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>1A, 1B, 1C, 1D, 2A, 2B1, 2B2, 3, 4, 5, 6A, 6B, 6C, 6D, 6E, 6F, 7</t>
-        </is>
-      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -1382,11 +1247,6 @@
           <t>170</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>1A1, 1A2, 1B, 2</t>
-        </is>
-      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -1394,11 +1254,6 @@
           <t>171</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>1, 2A, 2B, 2C, 3, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -1406,11 +1261,6 @@
           <t>172</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13, 14, 15, 16A, 16B, 16C, 16D, 16E, 16F, 16G, 16H, 16I, 2, 3, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -1418,11 +1268,6 @@
           <t>173</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>1A, 1B, 2A, 2B, 3, 4A, 4B, 5A, 5B, 6, 7A, 7B, 8A, 8B1, 8B2, 8C</t>
-        </is>
-      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -1430,11 +1275,6 @@
           <t>174</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>1, 2A1, 2A2, 2A3, 2A4, 2B</t>
-        </is>
-      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -1442,11 +1282,6 @@
           <t>175</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>1, 10, 11A, 11B, 11C1, 11C2, 11C3, 11C4, 12, 2A, 2B1, 2B2, 3, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -1454,11 +1289,6 @@
           <t>176</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12A, 12B, 13, 14, 15A, 15B, 15C, 16, 17, 2, 3, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -1466,11 +1296,6 @@
           <t>177</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>10A, 10B, 10C, 10D, 10E, 11, 12, 13, 1A, 1B, 1C, 1D, 2, 3, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -1478,11 +1303,6 @@
           <t>178</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 2, 3, 4, 5, 6, 7A, 7B, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -1490,11 +1310,6 @@
           <t>179</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>1, 10, 11A, 11B, 12, 2, 3, 4, 5, 6, 7A, 7B, 8A, 8B, 9</t>
-        </is>
-      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -1502,11 +1317,6 @@
           <t>18</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13A, 13B, 2, 3, 4, 5A, 5B, 5C, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -1514,11 +1324,6 @@
           <t>180</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 2, 3, 4, 5, 6, 7A, 7B, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -1526,11 +1331,6 @@
           <t>181</t>
         </is>
       </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18A, 18B, 2, 3, 4, 5, 6, 7, 8, 9A, 9B</t>
-        </is>
-      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -1538,11 +1338,6 @@
           <t>182</t>
         </is>
       </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13, 14, 15, 16, 17A, 17B, 17C, 18, 19, 2, 20, 21, 22, 23, 3, 4, 5, 6, 7A1, 7A2, 7B, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -1550,11 +1345,6 @@
           <t>183</t>
         </is>
       </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>1, 2, 3, 4, 5, 6A1, 6A2, 6B1, 6B2, 6B3, 6C1, 6C2, 6C3, 6D1, 6D2, 6D3, 6D4, 7A, 7B, 8A, 8B, 8C, 9A, 9B</t>
-        </is>
-      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -1562,11 +1352,6 @@
           <t>184</t>
         </is>
       </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13, 14, 15, 2, 3, 4, 5A, 5B, 6, 7A, 7B, 7C, 7D, 7E, 7F1, 7F2, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -1574,11 +1359,6 @@
           <t>185</t>
         </is>
       </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13, 14A1, 14A2, 14B, 15, 16A, 16B, 17, 18, 19, 20, 2A, 2B, 2C, 2D, 2E, 2F, 2G, 3, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -1586,11 +1366,6 @@
           <t>186</t>
         </is>
       </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -1598,11 +1373,6 @@
           <t>187</t>
         </is>
       </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -1610,11 +1380,6 @@
           <t>188</t>
         </is>
       </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -1622,11 +1387,6 @@
           <t>189</t>
         </is>
       </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>10, 11, 12, 13, 14, 15, 16, 17, 18, 1A, 1B, 1C, 1D, 1E, 1F, 2, 3, 4, 5, 6, 7A, 7B, 7C, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -1634,11 +1394,6 @@
           <t>19</t>
         </is>
       </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>1, 2</t>
-        </is>
-      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -1646,11 +1401,6 @@
           <t>190</t>
         </is>
       </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 20, 21, 22, 23, 2A, 2B, 2C, 3, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -1658,11 +1408,6 @@
           <t>191</t>
         </is>
       </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12A, 12B, 12C, 13, 2, 3, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -1670,11 +1415,6 @@
           <t>192</t>
         </is>
       </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13, 14, 15, 16, 2, 3, 4, 5, 6, 7, 8, 9A, 9B</t>
-        </is>
-      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -1682,11 +1422,6 @@
           <t>193</t>
         </is>
       </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13A, 13B, 14, 15, 16, 17, 18, 19A, 19B, 2, 20, 21, 22, 23, 24, 25, 26, 3, 4, 5, 6A, 6B, 6C, 6D, 6E, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -1694,11 +1429,6 @@
           <t>194</t>
         </is>
       </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 20, 21, 22, 23, 24, 25, 26, 27, 28, 29, 2A, 2B, 30, 31, 32, 33, 34, 35, 36, 3A, 3B, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -1706,11 +1436,6 @@
           <t>195</t>
         </is>
       </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>1, 10, 11A, 11B, 11C, 11D, 11E, 12, 13A, 13B, 14, 15, 16, 17, 18, 19, 2, 20, 21, 22, 3, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -1718,11 +1443,6 @@
           <t>196</t>
         </is>
       </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>1, 2, 3</t>
-        </is>
-      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -1730,11 +1450,6 @@
           <t>197</t>
         </is>
       </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>1, 2, 3</t>
-        </is>
-      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -1742,11 +1457,6 @@
           <t>198</t>
         </is>
       </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -1754,11 +1464,6 @@
           <t>199</t>
         </is>
       </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>1, 2</t>
-        </is>
-      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -1766,11 +1471,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>1, 2, 3, 4, 5, 6A, 6B, 6C, 7, 8A, 8B, 8C</t>
-        </is>
-      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -1778,11 +1478,6 @@
           <t>20</t>
         </is>
       </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>1, 2</t>
-        </is>
-      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -1790,11 +1485,6 @@
           <t>200</t>
         </is>
       </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 2, 3, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -1802,11 +1492,6 @@
           <t>201</t>
         </is>
       </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>1, 2</t>
-        </is>
-      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -1814,11 +1499,6 @@
           <t>202</t>
         </is>
       </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>1, 2</t>
-        </is>
-      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -1826,11 +1506,6 @@
           <t>203</t>
         </is>
       </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>1, 2A1, 2A2, 2A3, 2A4, 2A5, 2A6, 2A7, 2B, 3, 4</t>
-        </is>
-      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -1838,11 +1513,6 @@
           <t>204</t>
         </is>
       </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -1850,11 +1520,6 @@
           <t>205</t>
         </is>
       </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>1, 2</t>
-        </is>
-      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -1862,11 +1527,6 @@
           <t>206</t>
         </is>
       </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -1874,11 +1534,6 @@
           <t>207</t>
         </is>
       </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -1886,11 +1541,6 @@
           <t>208</t>
         </is>
       </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -1898,11 +1548,6 @@
           <t>209</t>
         </is>
       </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -1910,11 +1555,6 @@
           <t>21</t>
         </is>
       </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -1922,11 +1562,6 @@
           <t>210</t>
         </is>
       </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -1934,11 +1569,6 @@
           <t>211</t>
         </is>
       </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -1946,11 +1576,6 @@
           <t>212</t>
         </is>
       </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -1958,11 +1583,6 @@
           <t>213</t>
         </is>
       </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -1970,11 +1590,6 @@
           <t>214</t>
         </is>
       </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>1, 2</t>
-        </is>
-      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -1982,11 +1597,6 @@
           <t>215</t>
         </is>
       </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -1994,11 +1604,6 @@
           <t>216</t>
         </is>
       </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -2006,11 +1611,6 @@
           <t>217</t>
         </is>
       </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -2018,11 +1618,6 @@
           <t>218</t>
         </is>
       </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -2030,11 +1625,6 @@
           <t>219</t>
         </is>
       </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -2042,11 +1632,6 @@
           <t>22</t>
         </is>
       </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>1A, 1B, 1C, 1D1, 1D2, 1E1, 1E2, 1F, 2A, 2B, 3A, 3B, 4</t>
-        </is>
-      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -2054,11 +1639,6 @@
           <t>220</t>
         </is>
       </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -2066,11 +1646,6 @@
           <t>221</t>
         </is>
       </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>1A, 1B, 2A, 3, 4, 5, 6</t>
-        </is>
-      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -2078,11 +1653,6 @@
           <t>222</t>
         </is>
       </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13, 14, 15, 2A, 3, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -2090,11 +1660,6 @@
           <t>223</t>
         </is>
       </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -2102,11 +1667,6 @@
           <t>224</t>
         </is>
       </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -2114,11 +1674,6 @@
           <t>225</t>
         </is>
       </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>1A, 2</t>
-        </is>
-      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -2126,11 +1681,6 @@
           <t>226</t>
         </is>
       </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>1, 2</t>
-        </is>
-      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -2138,11 +1688,6 @@
           <t>227</t>
         </is>
       </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -2150,11 +1695,6 @@
           <t>228</t>
         </is>
       </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -2162,11 +1702,6 @@
           <t>229</t>
         </is>
       </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -2174,11 +1709,6 @@
           <t>23</t>
         </is>
       </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>10, 1A, 1B, 1C, 1D, 1E, 1F, 2A, 2B, 3A, 3B, 3C, 3D, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -2186,11 +1716,6 @@
           <t>230</t>
         </is>
       </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -2198,11 +1723,6 @@
           <t>231</t>
         </is>
       </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -2210,11 +1730,6 @@
           <t>232</t>
         </is>
       </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -2222,11 +1737,6 @@
           <t>233</t>
         </is>
       </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>1, 2, 3</t>
-        </is>
-      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -2234,11 +1744,6 @@
           <t>234</t>
         </is>
       </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -2246,11 +1751,6 @@
           <t>235</t>
         </is>
       </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>1, 2, 3</t>
-        </is>
-      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -2258,11 +1758,6 @@
           <t>236</t>
         </is>
       </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -2270,11 +1765,6 @@
           <t>237</t>
         </is>
       </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -2282,11 +1772,6 @@
           <t>238</t>
         </is>
       </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -2294,11 +1779,6 @@
           <t>239</t>
         </is>
       </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -2306,11 +1786,6 @@
           <t>24</t>
         </is>
       </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>1, 10A, 10B, 11, 12A, 12B, 13, 14, 2, 3, 4, 5, 6A, 6B, 7A, 7B, 7C, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -2318,11 +1793,6 @@
           <t>240</t>
         </is>
       </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -2330,11 +1800,6 @@
           <t>241</t>
         </is>
       </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -2342,11 +1807,6 @@
           <t>242</t>
         </is>
       </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -2354,11 +1814,6 @@
           <t>243</t>
         </is>
       </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -2366,11 +1821,6 @@
           <t>244</t>
         </is>
       </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -2378,11 +1828,6 @@
           <t>245</t>
         </is>
       </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -2390,11 +1835,6 @@
           <t>246</t>
         </is>
       </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -2402,11 +1842,6 @@
           <t>247</t>
         </is>
       </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -2414,11 +1849,6 @@
           <t>248</t>
         </is>
       </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -2426,11 +1856,6 @@
           <t>249</t>
         </is>
       </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -2438,11 +1863,6 @@
           <t>25</t>
         </is>
       </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12A, 12B, 12C, 12D, 13, 14, 15, 2, 3, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -2450,11 +1870,6 @@
           <t>250</t>
         </is>
       </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -2462,11 +1877,6 @@
           <t>251</t>
         </is>
       </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -2474,11 +1884,6 @@
           <t>252</t>
         </is>
       </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -2486,11 +1891,6 @@
           <t>253</t>
         </is>
       </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -2498,11 +1898,6 @@
           <t>254</t>
         </is>
       </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>1, 2, 3, 4, 5, 6, 7</t>
-        </is>
-      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -2510,11 +1905,6 @@
           <t>255</t>
         </is>
       </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>1, 2, 3, 4, 5</t>
-        </is>
-      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -2522,11 +1912,6 @@
           <t>256</t>
         </is>
       </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>1B, 2, 3, 4, 5</t>
-        </is>
-      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -2534,11 +1919,6 @@
           <t>257</t>
         </is>
       </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>1, 2</t>
-        </is>
-      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -2546,11 +1926,6 @@
           <t>258</t>
         </is>
       </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -2558,11 +1933,6 @@
           <t>259</t>
         </is>
       </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>1A, 1B, 1C, 2, 3, 4, 5, 6</t>
-        </is>
-      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -2570,11 +1940,6 @@
           <t>26</t>
         </is>
       </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>10A, 10B, 10C, 10D, 10E, 10F, 10G, 10H, 10I, 11A, 11B1, 11B2, 11C, 11D1, 11D2, 11E, 11F, 1A, 1B, 2, 3, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -2582,11 +1947,6 @@
           <t>260</t>
         </is>
       </c>
-      <c r="B181" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -2594,11 +1954,6 @@
           <t>261</t>
         </is>
       </c>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>1, 2, 3, 4, 5A, 5B</t>
-        </is>
-      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -2606,11 +1961,6 @@
           <t>262</t>
         </is>
       </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>1, 2, 3A, 3B, 3C, 3D, 4A</t>
-        </is>
-      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -2618,11 +1968,6 @@
           <t>263</t>
         </is>
       </c>
-      <c r="B184" t="inlineStr">
-        <is>
-          <t>1A1, 1A2, 1B1A1, 1B1A2, 1B1B, 1B2A1, 1B2A2, 1B2B, 2, 3A, 3B, 3C, 4A1, 4A2, 4B, 5</t>
-        </is>
-      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -2630,11 +1975,6 @@
           <t>264</t>
         </is>
       </c>
-      <c r="B185" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -2642,11 +1982,6 @@
           <t>265</t>
         </is>
       </c>
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -2654,11 +1989,6 @@
           <t>266</t>
         </is>
       </c>
-      <c r="B187" t="inlineStr">
-        <is>
-          <t>1A, 2A, 2B, 3, 4A, 4B1, 4B2, 5A, 5B, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -2666,11 +1996,6 @@
           <t>267</t>
         </is>
       </c>
-      <c r="B188" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -2678,11 +2003,6 @@
           <t>268</t>
         </is>
       </c>
-      <c r="B189" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -2690,11 +2010,6 @@
           <t>269</t>
         </is>
       </c>
-      <c r="B190" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -2702,11 +2017,6 @@
           <t>27</t>
         </is>
       </c>
-      <c r="B191" t="inlineStr">
-        <is>
-          <t>10, 11A1, 11A2, 11A3, 11A4, 11A5, 11B, 1A, 1B, 2A, 2B, 2C, 2D, 3, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -2714,11 +2024,6 @@
           <t>270</t>
         </is>
       </c>
-      <c r="B192" t="inlineStr">
-        <is>
-          <t>1, 2A, 2B, 3A, 3B</t>
-        </is>
-      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -2726,11 +2031,6 @@
           <t>271</t>
         </is>
       </c>
-      <c r="B193" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -2738,11 +2038,6 @@
           <t>272</t>
         </is>
       </c>
-      <c r="B194" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -2750,11 +2045,6 @@
           <t>273</t>
         </is>
       </c>
-      <c r="B195" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -2762,11 +2052,6 @@
           <t>274</t>
         </is>
       </c>
-      <c r="B196" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -2774,11 +2059,6 @@
           <t>28</t>
         </is>
       </c>
-      <c r="B197" t="inlineStr">
-        <is>
-          <t>1A, 1B, 1C, 1D, 2, 3A1, 3A2, 3B, 3C1, 3C2, 4, 5, 6, 7, 8</t>
-        </is>
-      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -2786,11 +2066,6 @@
           <t>29</t>
         </is>
       </c>
-      <c r="B198" t="inlineStr">
-        <is>
-          <t>1, 2A1, 2A2, 2A3, 2A4, 2B, 2C, 2D, 2E, 3</t>
-        </is>
-      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -2798,11 +2073,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="B199" t="inlineStr">
-        <is>
-          <t>1, 2, 3A, 3B, 4</t>
-        </is>
-      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -2810,11 +2080,6 @@
           <t>30</t>
         </is>
       </c>
-      <c r="B200" t="inlineStr">
-        <is>
-          <t>1, 2, 3, 4, 5A, 5B</t>
-        </is>
-      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -2822,11 +2087,6 @@
           <t>31</t>
         </is>
       </c>
-      <c r="B201" t="inlineStr">
-        <is>
-          <t>1A1, 1A2, 1B, 2A1, 2A2, 2A3, 2B, 3A1, 3A2, 3B, 4, 5, 6, 7A, 7B, 7C, 7D1, 7D2, 7D3</t>
-        </is>
-      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -2834,11 +2094,6 @@
           <t>32</t>
         </is>
       </c>
-      <c r="B202" t="inlineStr">
-        <is>
-          <t>1, 2, 3, 4, 5A, 5B, 5C, 5D, 5E, 6</t>
-        </is>
-      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -2846,11 +2101,6 @@
           <t>33</t>
         </is>
       </c>
-      <c r="B203" t="inlineStr">
-        <is>
-          <t>1, 2, 3, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -2858,11 +2108,6 @@
           <t>34</t>
         </is>
       </c>
-      <c r="B204" t="inlineStr">
-        <is>
-          <t>1, 2, 3, 4, 5</t>
-        </is>
-      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -2870,11 +2115,6 @@
           <t>35</t>
         </is>
       </c>
-      <c r="B205" t="inlineStr">
-        <is>
-          <t>1, 2, 3A, 3B, 3C1, 3C2, 3C3, 3C4, 3C5</t>
-        </is>
-      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -2882,11 +2122,6 @@
           <t>36</t>
         </is>
       </c>
-      <c r="B206" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -2894,11 +2129,6 @@
           <t>37</t>
         </is>
       </c>
-      <c r="B207" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 2, 3, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -2906,11 +2136,6 @@
           <t>38</t>
         </is>
       </c>
-      <c r="B208" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -2918,11 +2143,6 @@
           <t>39</t>
         </is>
       </c>
-      <c r="B209" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -2930,11 +2150,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="B210" t="inlineStr">
-        <is>
-          <t>1, 2A, 2B</t>
-        </is>
-      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -2942,11 +2157,6 @@
           <t>40</t>
         </is>
       </c>
-      <c r="B211" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -2954,11 +2164,6 @@
           <t>41</t>
         </is>
       </c>
-      <c r="B212" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -2966,11 +2171,6 @@
           <t>42</t>
         </is>
       </c>
-      <c r="B213" t="inlineStr">
-        <is>
-          <t>1, 2</t>
-        </is>
-      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -2978,11 +2178,6 @@
           <t>43</t>
         </is>
       </c>
-      <c r="B214" t="inlineStr">
-        <is>
-          <t>1, 2</t>
-        </is>
-      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -2990,11 +2185,6 @@
           <t>44</t>
         </is>
       </c>
-      <c r="B215" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 2, 22, 3, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -3002,11 +2192,6 @@
           <t>45</t>
         </is>
       </c>
-      <c r="B216" t="inlineStr">
-        <is>
-          <t>1, 2, 3A, 3B, 3C, 3D, 3E, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -3014,11 +2199,6 @@
           <t>46</t>
         </is>
       </c>
-      <c r="B217" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 20, 21, 22, 23, 24, 25, 26, 2A, 2B, 3, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -3026,11 +2206,6 @@
           <t>47</t>
         </is>
       </c>
-      <c r="B218" t="inlineStr">
-        <is>
-          <t>1, 10, 11A, 11B, 11C, 11D, 11E, 11F, 11G, 12, 13, 14, 15, 16, 17, 18, 19, 2, 20, 21, 22, 3A, 3B, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -3038,11 +2213,6 @@
           <t>48</t>
         </is>
       </c>
-      <c r="B219" t="inlineStr">
-        <is>
-          <t>10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 1A, 1B, 1C, 1D, 2, 20, 21, 22, 23, 24, 25, 26, 27, 28, 29, 3, 30, 31, 32, 33, 34, 35, 36, 37, 38, 39, 4, 40, 41, 42, 43, 44, 45, 46, 47A, 47B, 47C, 47D, 47E, 47F, 48, 49, 5, 50, 51, 52, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -3050,11 +2220,6 @@
           <t>49</t>
         </is>
       </c>
-      <c r="B220" t="inlineStr">
-        <is>
-          <t>10, 11, 12A, 13A, 13B, 14A, 14B, 15, 16A, 16B, 17, 18, 19A, 19B, 1A, 2, 20A, 20B, 21A, 21B, 21C, 22A, 22B, 23A, 23B, 24, 25, 26, 3, 37, 38, 39, 4, 40, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -3062,11 +2227,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="B221" t="inlineStr">
-        <is>
-          <t>1A, 1B, 2A, 2B, 2C, 3A, 3B, 3C</t>
-        </is>
-      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -3074,11 +2234,6 @@
           <t>50</t>
         </is>
       </c>
-      <c r="B222" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12A, 12B, 13, 14, 15, 16, 17, 18, 19, 2, 20A, 20B, 20C, 21, 22A, 22B, 23, 24, 25, 26, 27, 28, 29, 3, 30, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -3086,11 +2241,6 @@
           <t>51</t>
         </is>
       </c>
-      <c r="B223" t="inlineStr">
-        <is>
-          <t>1, 10, 11A, 11B, 11C, 11D, 11E, 11F, 12, 13, 14, 15A, 15B, 16A, 16B, 16C, 17, 18, 19, 2, 20, 21, 22, 23, 24, 25A, 25B, 26, 27, 28, 29, 3, 30, 4, 5, 6A, 6B, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -3098,11 +2248,6 @@
           <t>52</t>
         </is>
       </c>
-      <c r="B224" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 2, 3, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -3110,11 +2255,6 @@
           <t>53</t>
         </is>
       </c>
-      <c r="B225" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -3122,11 +2262,6 @@
           <t>54</t>
         </is>
       </c>
-      <c r="B226" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -3134,11 +2269,6 @@
           <t>55</t>
         </is>
       </c>
-      <c r="B227" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -3146,11 +2276,6 @@
           <t>56</t>
         </is>
       </c>
-      <c r="B228" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -3158,11 +2283,6 @@
           <t>57</t>
         </is>
       </c>
-      <c r="B229" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -3170,11 +2290,6 @@
           <t>58</t>
         </is>
       </c>
-      <c r="B230" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -3182,11 +2297,6 @@
           <t>59</t>
         </is>
       </c>
-      <c r="B231" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -3194,11 +2304,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B232" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12A, 12B, 12C, 13A, 13B, 13C, 2, 3, 4A, 4B, 4C, 5A, 5B, 5C, 6, 7A, 7B, 7C, 8, 9A, 9B</t>
-        </is>
-      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -3206,11 +2311,6 @@
           <t>60</t>
         </is>
       </c>
-      <c r="B233" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -3218,11 +2318,6 @@
           <t>61</t>
         </is>
       </c>
-      <c r="B234" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13A1, 13A2, 13B, 14, 15, 2, 3, 4, 5, 6, 7, 8A, 8B, 9</t>
-        </is>
-      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -3230,11 +2325,6 @@
           <t>62</t>
         </is>
       </c>
-      <c r="B235" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -3242,11 +2332,6 @@
           <t>63</t>
         </is>
       </c>
-      <c r="B236" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13A, 13B, 14A, 14B, 15, 16, 17, 18, 19, 2, 20, 21, 22, 23, 24, 25, 3, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -3254,11 +2339,6 @@
           <t>64</t>
         </is>
       </c>
-      <c r="B237" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -3266,11 +2346,6 @@
           <t>65</t>
         </is>
       </c>
-      <c r="B238" t="inlineStr">
-        <is>
-          <t>10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 1A, 1B, 2, 20, 21, 22, 23, 24, 25, 26, 27, 28, 29, 3, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -3278,11 +2353,6 @@
           <t>66</t>
         </is>
       </c>
-      <c r="B239" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -3290,11 +2360,6 @@
           <t>67</t>
         </is>
       </c>
-      <c r="B240" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -3302,11 +2367,6 @@
           <t>68</t>
         </is>
       </c>
-      <c r="B241" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -3314,11 +2374,6 @@
           <t>69</t>
         </is>
       </c>
-      <c r="B242" t="inlineStr">
-        <is>
-          <t>10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 1A1A, 1A1B, 1A2, 1B, 1C, 1D, 2, 20, 21, 22, 23, 24, 25, 3A1, 3A2, 3A3, 3A4, 3B, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -3326,11 +2381,6 @@
           <t>7</t>
         </is>
       </c>
-      <c r="B243" t="inlineStr">
-        <is>
-          <t>1A, 1B, 1C, 2A, 2B, 3, 4, 5, 6</t>
-        </is>
-      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -3338,11 +2388,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="B244" t="inlineStr">
-        <is>
-          <t>1, 2, 3, 4</t>
-        </is>
-      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -3350,11 +2395,6 @@
           <t>71</t>
         </is>
       </c>
-      <c r="B245" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 2, 20, 21, 22, 23, 24, 25, 26, 3, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -3362,11 +2402,6 @@
           <t>72</t>
         </is>
       </c>
-      <c r="B246" t="inlineStr">
-        <is>
-          <t>1, 2</t>
-        </is>
-      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -3374,11 +2409,6 @@
           <t>73</t>
         </is>
       </c>
-      <c r="B247" t="inlineStr">
-        <is>
-          <t>1A, 1B, 1C, 1D, 1E, 2A, 2B, 2C, 2D, 3, 4A, 4B, 5A1, 5A2, 5B, 5C</t>
-        </is>
-      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -3386,11 +2416,6 @@
           <t>74</t>
         </is>
       </c>
-      <c r="B248" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -3398,11 +2423,6 @@
           <t>75</t>
         </is>
       </c>
-      <c r="B249" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -3410,11 +2430,6 @@
           <t>76</t>
         </is>
       </c>
-      <c r="B250" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -3422,11 +2437,6 @@
           <t>77</t>
         </is>
       </c>
-      <c r="B251" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -3434,11 +2444,6 @@
           <t>78</t>
         </is>
       </c>
-      <c r="B252" t="inlineStr">
-        <is>
-          <t>1, 10, 2A1, 2A2, 2B, 2C, 3, 4A, 4B, 5, 6A, 6B, 7A, 7B, 7C, 7D, 7E, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -3446,11 +2451,6 @@
           <t>79</t>
         </is>
       </c>
-      <c r="B253" t="inlineStr">
-        <is>
-          <t>10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 1A, 1B, 2, 3A, 3B, 3C, 3D, 4, 5, 6, 7, 8, 9A, 9B</t>
-        </is>
-      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -3458,11 +2458,6 @@
           <t>8</t>
         </is>
       </c>
-      <c r="B254" t="inlineStr">
-        <is>
-          <t>1, 10A, 10B, 11, 12, 13, 14A, 14B, 2, 3, 4, 5, 6, 7, 8A, 8B, 9</t>
-        </is>
-      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -3470,11 +2465,6 @@
           <t>80</t>
         </is>
       </c>
-      <c r="B255" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 20A, 20B, 20C, 21, 22, 2A, 2B, 3, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -3482,11 +2472,6 @@
           <t>81</t>
         </is>
       </c>
-      <c r="B256" t="inlineStr">
-        <is>
-          <t>1, 2, 3, 4, 5, 6, 7</t>
-        </is>
-      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -3494,11 +2479,6 @@
           <t>82</t>
         </is>
       </c>
-      <c r="B257" t="inlineStr">
-        <is>
-          <t>1, 10, 11A, 11B, 12, 13, 14, 15, 2, 3A, 3B, 3C, 4, 5A, 5B, 5C, 5D, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -3506,11 +2486,6 @@
           <t>83</t>
         </is>
       </c>
-      <c r="B258" t="inlineStr">
-        <is>
-          <t>1, 10, 11A, 11B, 11C1, 11C2, 12A, 12B, 13A, 13B, 14, 15, 16, 17, 18A, 18B, 19, 2, 20A, 20B, 21, 3A, 3B, 3C, 4, 5A, 5B, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -3518,11 +2493,6 @@
           <t>84</t>
         </is>
       </c>
-      <c r="B259" t="inlineStr">
-        <is>
-          <t>10A, 10B, 11, 12, 13, 14, 15, 16, 17, 18, 19, 1A, 1B, 2, 20, 21, 22, 23, 24, 25, 26, 27, 28, 29, 3, 30, 31, 32A, 32B, 33, 34, 35, 36, 4, 5, 6, 7, 8, 9A, 9B</t>
-        </is>
-      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -3530,11 +2500,6 @@
           <t>85</t>
         </is>
       </c>
-      <c r="B260" t="inlineStr">
-        <is>
-          <t>10, 11, 12, 13, 14, 15, 16, 17, 18A, 18B, 18C, 19, 1A, 1B, 2, 3A1, 3A2, 3B, 4, 5A, 5B, 5C, 6A, 6B, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -3542,11 +2507,6 @@
           <t>86</t>
         </is>
       </c>
-      <c r="B261" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -3554,11 +2514,6 @@
           <t>87</t>
         </is>
       </c>
-      <c r="B262" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -3566,11 +2521,6 @@
           <t>88</t>
         </is>
       </c>
-      <c r="B263" t="inlineStr">
-        <is>
-          <t>1A, 1B, 1C, 1D, 1E, 1F, 1G, 1H, 1I, 2, 3A, 3B, 3C, 3D, 4, 5A, 5B, 5C1, 5C2, 5D</t>
-        </is>
-      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -3578,11 +2528,6 @@
           <t>89</t>
         </is>
       </c>
-      <c r="B264" t="inlineStr">
-        <is>
-          <t>1, 2, 3</t>
-        </is>
-      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -3590,11 +2535,6 @@
           <t>9</t>
         </is>
       </c>
-      <c r="B265" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -3602,11 +2542,6 @@
           <t>90</t>
         </is>
       </c>
-      <c r="B266" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -3614,11 +2549,6 @@
           <t>91</t>
         </is>
       </c>
-      <c r="B267" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -3626,11 +2556,6 @@
           <t>92</t>
         </is>
       </c>
-      <c r="B268" t="inlineStr">
-        <is>
-          <t>1, 2, 3, 4A, 4B, 4C, 5, 6, 7, 8</t>
-        </is>
-      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -3638,11 +2563,6 @@
           <t>93</t>
         </is>
       </c>
-      <c r="B269" t="inlineStr">
-        <is>
-          <t>1, 2A, 2B, 3A1, 3A2, 3A3, 3B1, 3B2, 4A, 4B</t>
-        </is>
-      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -3650,11 +2570,6 @@
           <t>94</t>
         </is>
       </c>
-      <c r="B270" t="inlineStr">
-        <is>
-          <t>1, 2, 3A, 3B, 3C, 3D, 4</t>
-        </is>
-      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -3662,11 +2577,6 @@
           <t>95</t>
         </is>
       </c>
-      <c r="B271" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -3674,11 +2584,6 @@
           <t>96</t>
         </is>
       </c>
-      <c r="B272" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13, 14, 15, 16A, 16B, 17, 18, 19A, 19B, 2, 20, 21A, 21B1, 21B2, 22, 23, 24A, 24B, 24C, 25, 26, 3, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -3686,11 +2591,6 @@
           <t>97</t>
         </is>
       </c>
-      <c r="B273" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 2, 3, 4A, 4B, 5, 6A, 6B, 6C, 6D, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -3698,21 +2598,11 @@
           <t>98</t>
         </is>
       </c>
-      <c r="B274" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 2, 3, 4A, 4B, 5A, 5B, 6, 7A, 7B, 8A, 8B, 9</t>
-        </is>
-      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
           <t>99</t>
-        </is>
-      </c>
-      <c r="B275" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13, 14, 15A, 15B, 16, 2A, 2B, 3, 4, 5, 6, 7, 8, 9</t>
         </is>
       </c>
     </row>

--- a/out/Village_map_of_Tiruvallur_Gummidipoondi_Manellore_13.455683_80.019989.xlsx
+++ b/out/Village_map_of_Tiruvallur_Gummidipoondi_Manellore_13.455683_80.019989.xlsx
@@ -1058,6 +1058,11 @@
           <t>146</t>
         </is>
       </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 2, 20, 21, 22, 23, 24, 25, 26, 27A, 27B, 28, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1065,6 +1070,11 @@
           <t>147</t>
         </is>
       </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 2, 20, 21, 22, 23, 24, 3, 4, 5, 6, 7A, 7B, 7C, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1072,6 +1082,11 @@
           <t>148</t>
         </is>
       </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B, 2C, 2D, 2E, 2F, 3A, 3B1, 3B2, 3C, 3D, 4A, 4B, 4C, 4D, 4E, 4F1, 4F2, 4F3, 4G, 4H, 5</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1079,6 +1094,11 @@
           <t>149</t>
         </is>
       </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 2, 3, 4, 5A, 5B, 6</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1086,6 +1106,11 @@
           <t>15</t>
         </is>
       </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>1, 10A, 10B, 11, 12, 13, 14, 15, 16, 17, 18, 19, 20, 21A, 21B, 22A, 22B, 22C, 22D, 22E, 22F, 22G, 22H, 23, 24, 25, 26, 27, 2A, 2B, 3A, 3B, 4, 5A, 5B, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1093,6 +1118,11 @@
           <t>150</t>
         </is>
       </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>1, 2, 3A1, 3A2, 3B1, 3B2, 3C1, 3C2, 3D, 3E1, 3E2, 3E3, 3F, 4, 5, 6, 7</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1100,6 +1130,11 @@
           <t>151</t>
         </is>
       </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16A, 16B, 17, 18, 19A, 19B, 20, 21, 2A, 2B, 3, 4, 5A, 5B1, 5B2, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1107,6 +1142,11 @@
           <t>152</t>
         </is>
       </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 2, 20, 21, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1114,6 +1154,11 @@
           <t>153</t>
         </is>
       </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13A1, 13A2, 13B, 14, 2A, 2B, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -1121,6 +1166,11 @@
           <t>154</t>
         </is>
       </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>1, 10, 11A, 11B1, 11B2, 12A, 12B1, 12B2, 13, 14A1, 14A2, 14B, 15A1, 15A2, 15B, 16A, 16B, 17A, 17B, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1128,6 +1178,11 @@
           <t>155</t>
         </is>
       </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>1, 10A1, 10A2, 10A3, 10B, 10C, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -1135,6 +1190,11 @@
           <t>156</t>
         </is>
       </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -1142,6 +1202,11 @@
           <t>157</t>
         </is>
       </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 2, 20, 21A, 21B, 22, 23, 24, 25, 26, 27, 28, 29, 30, 3A, 3B, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -1149,6 +1214,11 @@
           <t>158</t>
         </is>
       </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14A, 14B, 15, 16, 17, 18, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -1156,6 +1226,11 @@
           <t>159</t>
         </is>
       </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -1163,6 +1238,11 @@
           <t>16</t>
         </is>
       </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12A, 12B, 13, 14, 15, 16, 17, 18, 19, 2, 20, 21, 22, 23, 24, 25, 3, 4, 5, 6, 7, 8A, 8B, 9</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -1170,6 +1250,11 @@
           <t>160</t>
         </is>
       </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 13, 14, 15, 16, 17, 1A, 1B, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -1177,6 +1262,11 @@
           <t>161</t>
         </is>
       </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4A, 4B, 5, 6, 7, 8</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -1184,6 +1274,11 @@
           <t>162</t>
         </is>
       </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 2, 20, 21, 22, 23, 3A, 3B, 4A, 4B, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -1191,6 +1286,11 @@
           <t>163</t>
         </is>
       </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>10, 11, 12A, 12B, 12C, 12D, 1A, 1B, 2A, 2B1, 2B2, 3, 4, 5, 6, 7, 8A, 8B, 9</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -1198,6 +1298,11 @@
           <t>164</t>
         </is>
       </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>1, 10, 2A1, 2A2, 2B, 3, 4, 5A, 5B, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -1205,6 +1310,11 @@
           <t>165</t>
         </is>
       </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15A1, 15A2, 15B, 15C1, 15C2, 16, 17, 18A, 18B1, 18B2, 2, 3, 4, 5, 6, 7A, 7B, 7C, 7D, 7E, 8, 9A, 9B</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -1212,6 +1322,11 @@
           <t>166</t>
         </is>
       </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>1, 10, 11A, 11B, 12A, 12B, 13, 14, 15, 16A, 16B, 16C, 17, 18, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -1219,6 +1334,11 @@
           <t>167</t>
         </is>
       </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12A, 12B, 13A, 13B, 14, 15, 16, 17, 18, 2, 3A1, 3A2, 3B, 3C, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -1226,6 +1346,11 @@
           <t>168</t>
         </is>
       </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>1, 10A, 10B, 11A, 11B, 12, 13, 14, 15, 16, 2, 3, 4, 5, 6A, 6B, 7, 8, 9A, 9B, 9C, 9D, 9E, 9F</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -1233,6 +1358,11 @@
           <t>169</t>
         </is>
       </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 1A, 1B, 1C, 1D, 2, 20, 3, 4, 5, 6, 7, 8A, 8B, 9</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -1240,6 +1370,11 @@
           <t>17</t>
         </is>
       </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 1D, 2A, 2B1, 2B2, 3, 4, 5, 6A, 6B, 6C, 6D, 6E, 6F, 7</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -1247,6 +1382,11 @@
           <t>170</t>
         </is>
       </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>1A1, 1A2, 1B, 2</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -1254,6 +1394,11 @@
           <t>171</t>
         </is>
       </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B, 2C, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -1261,6 +1406,11 @@
           <t>172</t>
         </is>
       </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16A, 16B, 16C, 16D, 16E, 16F, 16G, 16H, 16I, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -1268,6 +1418,11 @@
           <t>173</t>
         </is>
       </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2A, 2B, 3, 4A, 4B, 5A, 5B, 6, 7A, 7B, 8A, 8B1, 8B2, 8C</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -1275,6 +1430,11 @@
           <t>174</t>
         </is>
       </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>1, 2A1, 2A2, 2A3, 2A4, 2B</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -1282,6 +1442,11 @@
           <t>175</t>
         </is>
       </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>1, 10, 11A, 11B, 11C1, 11C2, 11C3, 11C4, 12, 2A, 2B1, 2B2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -1289,6 +1454,11 @@
           <t>176</t>
         </is>
       </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12A, 12B, 13, 14, 15A, 15B, 15C, 16, 17, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -1296,6 +1466,11 @@
           <t>177</t>
         </is>
       </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>10A, 10B, 10C, 10D, 10E, 11, 12, 13, 1A, 1B, 1C, 1D, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -1303,6 +1478,11 @@
           <t>178</t>
         </is>
       </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 2, 3, 4, 5, 6, 7A, 7B, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -1310,6 +1490,11 @@
           <t>179</t>
         </is>
       </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>1, 10, 11A, 11B, 12, 2, 3, 4, 5, 6, 7A, 7B, 8A, 8B, 9</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -1317,6 +1502,11 @@
           <t>18</t>
         </is>
       </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13A, 13B, 2, 3, 4, 5A, 5B, 5C, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -1324,6 +1514,11 @@
           <t>180</t>
         </is>
       </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 2, 3, 4, 5, 6, 7A, 7B, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -1331,6 +1526,11 @@
           <t>181</t>
         </is>
       </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18A, 18B, 2, 3, 4, 5, 6, 7, 8, 9A, 9B</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -1338,6 +1538,11 @@
           <t>182</t>
         </is>
       </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17A, 17B, 17C, 18, 19, 2, 20, 21, 22, 23, 3, 4, 5, 6, 7A1, 7A2, 7B, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -1345,6 +1550,11 @@
           <t>183</t>
         </is>
       </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6A1, 6A2, 6B1, 6B2, 6B3, 6C1, 6C2, 6C3, 6D1, 6D2, 6D3, 6D4, 7A, 7B, 8A, 8B, 8C, 9A, 9B</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -1352,6 +1562,11 @@
           <t>184</t>
         </is>
       </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 2, 3, 4, 5A, 5B, 6, 7A, 7B, 7C, 7D, 7E, 7F1, 7F2, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -1359,6 +1574,11 @@
           <t>185</t>
         </is>
       </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14A1, 14A2, 14B, 15, 16A, 16B, 17, 18, 19, 20, 2A, 2B, 2C, 2D, 2E, 2F, 2G, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -1366,6 +1586,11 @@
           <t>186</t>
         </is>
       </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -1373,6 +1598,11 @@
           <t>187</t>
         </is>
       </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -1380,6 +1610,11 @@
           <t>188</t>
         </is>
       </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -1387,6 +1622,11 @@
           <t>189</t>
         </is>
       </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 13, 14, 15, 16, 17, 18, 1A, 1B, 1C, 1D, 1E, 1F, 2, 3, 4, 5, 6, 7A, 7B, 7C, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -1394,6 +1634,11 @@
           <t>19</t>
         </is>
       </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -1401,6 +1646,11 @@
           <t>190</t>
         </is>
       </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 20, 21, 22, 23, 2A, 2B, 2C, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -1408,6 +1658,11 @@
           <t>191</t>
         </is>
       </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12A, 12B, 12C, 13, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -1415,6 +1670,11 @@
           <t>192</t>
         </is>
       </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 2, 3, 4, 5, 6, 7, 8, 9A, 9B</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -1422,6 +1682,11 @@
           <t>193</t>
         </is>
       </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13A, 13B, 14, 15, 16, 17, 18, 19A, 19B, 2, 20, 21, 22, 23, 24, 25, 26, 3, 4, 5, 6A, 6B, 6C, 6D, 6E, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -1429,6 +1694,11 @@
           <t>194</t>
         </is>
       </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 20, 21, 22, 23, 24, 25, 26, 27, 28, 29, 2A, 2B, 30, 31, 32, 33, 34, 35, 36, 3A, 3B, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -1436,6 +1706,11 @@
           <t>195</t>
         </is>
       </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>1, 10, 11A, 11B, 11C, 11D, 11E, 12, 13A, 13B, 14, 15, 16, 17, 18, 19, 2, 20, 21, 22, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -1443,6 +1718,11 @@
           <t>196</t>
         </is>
       </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>1, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -1450,6 +1730,11 @@
           <t>197</t>
         </is>
       </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>1, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -1457,6 +1742,11 @@
           <t>198</t>
         </is>
       </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -1464,6 +1754,11 @@
           <t>199</t>
         </is>
       </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -1471,6 +1766,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6A, 6B, 6C, 7, 8A, 8B, 8C</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -1478,6 +1778,11 @@
           <t>20</t>
         </is>
       </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -1485,6 +1790,11 @@
           <t>200</t>
         </is>
       </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -1492,6 +1802,11 @@
           <t>201</t>
         </is>
       </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -1499,6 +1814,11 @@
           <t>202</t>
         </is>
       </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -1506,6 +1826,11 @@
           <t>203</t>
         </is>
       </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>1, 2A1, 2A2, 2A3, 2A4, 2A5, 2A6, 2A7, 2B, 3, 4</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -1513,6 +1838,11 @@
           <t>204</t>
         </is>
       </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -1520,6 +1850,11 @@
           <t>205</t>
         </is>
       </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -1527,6 +1862,11 @@
           <t>206</t>
         </is>
       </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -1534,6 +1874,11 @@
           <t>207</t>
         </is>
       </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -1541,6 +1886,11 @@
           <t>208</t>
         </is>
       </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -1548,6 +1898,11 @@
           <t>209</t>
         </is>
       </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -1555,6 +1910,11 @@
           <t>21</t>
         </is>
       </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -1562,6 +1922,11 @@
           <t>210</t>
         </is>
       </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -1569,6 +1934,11 @@
           <t>211</t>
         </is>
       </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -1576,6 +1946,11 @@
           <t>212</t>
         </is>
       </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -1583,6 +1958,11 @@
           <t>213</t>
         </is>
       </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -1590,6 +1970,11 @@
           <t>214</t>
         </is>
       </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -1597,6 +1982,11 @@
           <t>215</t>
         </is>
       </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -1604,6 +1994,11 @@
           <t>216</t>
         </is>
       </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -1611,6 +2006,11 @@
           <t>217</t>
         </is>
       </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -1618,6 +2018,11 @@
           <t>218</t>
         </is>
       </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -1625,6 +2030,11 @@
           <t>219</t>
         </is>
       </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -1632,6 +2042,11 @@
           <t>22</t>
         </is>
       </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 1D1, 1D2, 1E1, 1E2, 1F, 2A, 2B, 3A, 3B, 4</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -1639,6 +2054,11 @@
           <t>220</t>
         </is>
       </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -1646,6 +2066,11 @@
           <t>221</t>
         </is>
       </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2A, 3, 4, 5, 6</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -1653,6 +2078,11 @@
           <t>222</t>
         </is>
       </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 2A, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -1660,6 +2090,11 @@
           <t>223</t>
         </is>
       </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -1667,6 +2102,11 @@
           <t>224</t>
         </is>
       </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -1674,11 +2114,21 @@
           <t>225</t>
         </is>
       </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>1A, 2</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
           <t>226</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>1, 2</t>
         </is>
       </c>
     </row>

--- a/out/Village_map_of_Tiruvallur_Gummidipoondi_Manellore_13.455683_80.019989.xlsx
+++ b/out/Village_map_of_Tiruvallur_Gummidipoondi_Manellore_13.455683_80.019989.xlsx
@@ -2138,6 +2138,11 @@
           <t>227</t>
         </is>
       </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -2145,6 +2150,11 @@
           <t>228</t>
         </is>
       </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -2152,6 +2162,11 @@
           <t>229</t>
         </is>
       </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -2159,6 +2174,11 @@
           <t>23</t>
         </is>
       </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>10, 1A, 1B, 1C, 1D, 1E, 1F, 2A, 2B, 3A, 3B, 3C, 3D, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -2166,6 +2186,11 @@
           <t>230</t>
         </is>
       </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -2173,6 +2198,11 @@
           <t>231</t>
         </is>
       </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -2180,6 +2210,11 @@
           <t>232</t>
         </is>
       </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -2187,6 +2222,11 @@
           <t>233</t>
         </is>
       </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>1, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -2194,6 +2234,11 @@
           <t>234</t>
         </is>
       </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -2201,6 +2246,11 @@
           <t>235</t>
         </is>
       </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>1, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -2208,6 +2258,11 @@
           <t>236</t>
         </is>
       </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -2215,6 +2270,11 @@
           <t>237</t>
         </is>
       </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -2222,6 +2282,11 @@
           <t>238</t>
         </is>
       </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -2229,6 +2294,11 @@
           <t>239</t>
         </is>
       </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -2236,6 +2306,11 @@
           <t>24</t>
         </is>
       </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>1, 10A, 10B, 11, 12A, 12B, 13, 14, 2, 3, 4, 5, 6A, 6B, 7A, 7B, 7C, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -2243,6 +2318,11 @@
           <t>240</t>
         </is>
       </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -2250,6 +2330,11 @@
           <t>241</t>
         </is>
       </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -2257,6 +2342,11 @@
           <t>242</t>
         </is>
       </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -2264,6 +2354,11 @@
           <t>243</t>
         </is>
       </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -2271,6 +2366,11 @@
           <t>244</t>
         </is>
       </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -2278,6 +2378,11 @@
           <t>245</t>
         </is>
       </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -2285,6 +2390,11 @@
           <t>246</t>
         </is>
       </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -2292,6 +2402,11 @@
           <t>247</t>
         </is>
       </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -2299,6 +2414,11 @@
           <t>248</t>
         </is>
       </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -2306,6 +2426,11 @@
           <t>249</t>
         </is>
       </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -2313,6 +2438,11 @@
           <t>25</t>
         </is>
       </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12A, 12B, 12C, 12D, 13, 14, 15, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -2320,6 +2450,11 @@
           <t>250</t>
         </is>
       </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -2327,6 +2462,11 @@
           <t>251</t>
         </is>
       </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -2334,6 +2474,11 @@
           <t>252</t>
         </is>
       </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -2341,6 +2486,11 @@
           <t>253</t>
         </is>
       </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -2348,6 +2498,11 @@
           <t>254</t>
         </is>
       </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6, 7</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -2355,6 +2510,11 @@
           <t>255</t>
         </is>
       </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -2362,6 +2522,11 @@
           <t>256</t>
         </is>
       </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>1B, 2, 3, 4, 5</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -2369,6 +2534,11 @@
           <t>257</t>
         </is>
       </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -2376,6 +2546,11 @@
           <t>258</t>
         </is>
       </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -2383,6 +2558,11 @@
           <t>259</t>
         </is>
       </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 2, 3, 4, 5, 6</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -2390,6 +2570,11 @@
           <t>26</t>
         </is>
       </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>10A, 10B, 10C, 10D, 10E, 10F, 10G, 10H, 10I, 11A, 11B1, 11B2, 11C, 11D1, 11D2, 11E, 11F, 1A, 1B, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -2397,6 +2582,11 @@
           <t>260</t>
         </is>
       </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -2404,6 +2594,11 @@
           <t>261</t>
         </is>
       </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5A, 5B</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -2411,6 +2606,11 @@
           <t>262</t>
         </is>
       </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>1, 2, 3A, 3B, 3C, 3D, 4A</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -2418,6 +2618,11 @@
           <t>263</t>
         </is>
       </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>1A1, 1A2, 1B1A1, 1B1A2, 1B1B, 1B2A1, 1B2A2, 1B2B, 2, 3A, 3B, 3C, 4A1, 4A2, 4B, 5</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -2425,6 +2630,11 @@
           <t>264</t>
         </is>
       </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -2432,6 +2642,11 @@
           <t>265</t>
         </is>
       </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -2439,6 +2654,11 @@
           <t>266</t>
         </is>
       </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>1A, 2A, 2B, 3, 4A, 4B1, 4B2, 5A, 5B, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -2446,6 +2666,11 @@
           <t>267</t>
         </is>
       </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -2453,6 +2678,11 @@
           <t>268</t>
         </is>
       </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -2460,6 +2690,11 @@
           <t>269</t>
         </is>
       </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -2467,6 +2702,11 @@
           <t>27</t>
         </is>
       </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>10, 11A1, 11A2, 11A3, 11A4, 11A5, 11B, 1A, 1B, 2A, 2B, 2C, 2D, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -2474,6 +2714,11 @@
           <t>270</t>
         </is>
       </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B, 3A, 3B</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -2481,6 +2726,11 @@
           <t>271</t>
         </is>
       </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -2488,6 +2738,11 @@
           <t>272</t>
         </is>
       </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -2495,6 +2750,11 @@
           <t>273</t>
         </is>
       </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -2502,6 +2762,11 @@
           <t>274</t>
         </is>
       </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -2509,6 +2774,11 @@
           <t>28</t>
         </is>
       </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 1D, 2, 3A1, 3A2, 3B, 3C1, 3C2, 4, 5, 6, 7, 8</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -2516,6 +2786,11 @@
           <t>29</t>
         </is>
       </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>1, 2A1, 2A2, 2A3, 2A4, 2B, 2C, 2D, 2E, 3</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -2523,6 +2798,11 @@
           <t>3</t>
         </is>
       </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>1, 2, 3A, 3B, 4</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -2530,6 +2810,11 @@
           <t>30</t>
         </is>
       </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5A, 5B</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -2537,6 +2822,11 @@
           <t>31</t>
         </is>
       </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>1A1, 1A2, 1B, 2A1, 2A2, 2A3, 2B, 3A1, 3A2, 3B, 4, 5, 6, 7A, 7B, 7C, 7D1, 7D2, 7D3</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -2544,6 +2834,11 @@
           <t>32</t>
         </is>
       </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5A, 5B, 5C, 5D, 5E, 6</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -2551,6 +2846,11 @@
           <t>33</t>
         </is>
       </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -2558,6 +2858,11 @@
           <t>34</t>
         </is>
       </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -2565,6 +2870,11 @@
           <t>35</t>
         </is>
       </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>1, 2, 3A, 3B, 3C1, 3C2, 3C3, 3C4, 3C5</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -2572,6 +2882,11 @@
           <t>36</t>
         </is>
       </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -2579,6 +2894,11 @@
           <t>37</t>
         </is>
       </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -2586,6 +2906,11 @@
           <t>38</t>
         </is>
       </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -2593,6 +2918,11 @@
           <t>39</t>
         </is>
       </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -2600,6 +2930,11 @@
           <t>4</t>
         </is>
       </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -2607,6 +2942,11 @@
           <t>40</t>
         </is>
       </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -2614,6 +2954,11 @@
           <t>41</t>
         </is>
       </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -2621,6 +2966,11 @@
           <t>42</t>
         </is>
       </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -2628,6 +2978,11 @@
           <t>43</t>
         </is>
       </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -2635,6 +2990,11 @@
           <t>44</t>
         </is>
       </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 2, 22, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -2642,6 +3002,11 @@
           <t>45</t>
         </is>
       </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>1, 2, 3A, 3B, 3C, 3D, 3E, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -2649,6 +3014,11 @@
           <t>46</t>
         </is>
       </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 20, 21, 22, 23, 24, 25, 26, 2A, 2B, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -2656,6 +3026,11 @@
           <t>47</t>
         </is>
       </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>1, 10, 11A, 11B, 11C, 11D, 11E, 11F, 11G, 12, 13, 14, 15, 16, 17, 18, 19, 2, 20, 21, 22, 3A, 3B, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -2663,6 +3038,11 @@
           <t>48</t>
         </is>
       </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 1A, 1B, 1C, 1D, 2, 20, 21, 22, 23, 24, 25, 26, 27, 28, 29, 3, 30, 31, 32, 33, 34, 35, 36, 37, 38, 39, 4, 40, 41, 42, 43, 44, 45, 46, 47A, 47B, 47C, 47D, 47E, 47F, 48, 49, 5, 50, 51, 52, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -2670,6 +3050,11 @@
           <t>49</t>
         </is>
       </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>10, 11, 12A, 13A, 13B, 14A, 14B, 15, 16A, 16B, 17, 18, 19A, 19B, 1A, 2, 20A, 20B, 21A, 21B, 21C, 22A, 22B, 23A, 23B, 24, 25, 26, 3, 37, 38, 39, 4, 40, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -2677,6 +3062,11 @@
           <t>5</t>
         </is>
       </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2A, 2B, 2C, 3A, 3B, 3C</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -2684,6 +3074,11 @@
           <t>50</t>
         </is>
       </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12A, 12B, 13, 14, 15, 16, 17, 18, 19, 2, 20A, 20B, 20C, 21, 22A, 22B, 23, 24, 25, 26, 27, 28, 29, 3, 30, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -2691,6 +3086,11 @@
           <t>51</t>
         </is>
       </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>1, 10, 11A, 11B, 11C, 11D, 11E, 11F, 12, 13, 14, 15A, 15B, 16A, 16B, 16C, 17, 18, 19, 2, 20, 21, 22, 23, 24, 25A, 25B, 26, 27, 28, 29, 3, 30, 4, 5, 6A, 6B, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -2698,6 +3098,11 @@
           <t>52</t>
         </is>
       </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -2705,6 +3110,11 @@
           <t>53</t>
         </is>
       </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -2712,6 +3122,11 @@
           <t>54</t>
         </is>
       </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -2719,6 +3134,11 @@
           <t>55</t>
         </is>
       </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -2726,6 +3146,11 @@
           <t>56</t>
         </is>
       </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -2733,6 +3158,11 @@
           <t>57</t>
         </is>
       </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -2740,6 +3170,11 @@
           <t>58</t>
         </is>
       </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -2747,6 +3182,11 @@
           <t>59</t>
         </is>
       </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -2754,6 +3194,11 @@
           <t>6</t>
         </is>
       </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12A, 12B, 12C, 13A, 13B, 13C, 2, 3, 4A, 4B, 4C, 5A, 5B, 5C, 6, 7A, 7B, 7C, 8, 9A, 9B</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -2761,6 +3206,11 @@
           <t>60</t>
         </is>
       </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -2768,6 +3218,11 @@
           <t>61</t>
         </is>
       </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13A1, 13A2, 13B, 14, 15, 2, 3, 4, 5, 6, 7, 8A, 8B, 9</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -2775,6 +3230,11 @@
           <t>62</t>
         </is>
       </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -2782,11 +3242,21 @@
           <t>63</t>
         </is>
       </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13A, 13B, 14A, 14B, 15, 16, 17, 18, 19, 2, 20, 21, 22, 23, 24, 25, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
           <t>64</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>

--- a/out/Village_map_of_Tiruvallur_Gummidipoondi_Manellore_13.455683_80.019989.xlsx
+++ b/out/Village_map_of_Tiruvallur_Gummidipoondi_Manellore_13.455683_80.019989.xlsx
@@ -3266,6 +3266,11 @@
           <t>65</t>
         </is>
       </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 1A, 1B, 2, 20, 21, 22, 23, 24, 25, 26, 27, 28, 29, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -3273,6 +3278,11 @@
           <t>66</t>
         </is>
       </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -3280,6 +3290,11 @@
           <t>67</t>
         </is>
       </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -3287,6 +3302,11 @@
           <t>68</t>
         </is>
       </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -3294,6 +3314,11 @@
           <t>69</t>
         </is>
       </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 1A1A, 1A1B, 1A2, 1B, 1C, 1D, 2, 20, 21, 22, 23, 24, 25, 3A1, 3A2, 3A3, 3A4, 3B, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -3301,6 +3326,11 @@
           <t>7</t>
         </is>
       </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 2A, 2B, 3, 4, 5, 6</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -3308,6 +3338,11 @@
           <t>70</t>
         </is>
       </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -3315,6 +3350,11 @@
           <t>71</t>
         </is>
       </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 2, 20, 21, 22, 23, 24, 25, 26, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -3322,6 +3362,11 @@
           <t>72</t>
         </is>
       </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -3329,6 +3374,11 @@
           <t>73</t>
         </is>
       </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 1D, 1E, 2A, 2B, 2C, 2D, 3, 4A, 4B, 5A1, 5A2, 5B, 5C</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -3336,6 +3386,11 @@
           <t>74</t>
         </is>
       </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -3343,6 +3398,11 @@
           <t>75</t>
         </is>
       </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -3350,6 +3410,11 @@
           <t>76</t>
         </is>
       </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -3357,6 +3422,11 @@
           <t>77</t>
         </is>
       </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -3364,6 +3434,11 @@
           <t>78</t>
         </is>
       </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>1, 10, 2A1, 2A2, 2B, 2C, 3, 4A, 4B, 5, 6A, 6B, 7A, 7B, 7C, 7D, 7E, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -3371,6 +3446,11 @@
           <t>79</t>
         </is>
       </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 1A, 1B, 2, 3A, 3B, 3C, 3D, 4, 5, 6, 7, 8, 9A, 9B</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -3378,6 +3458,11 @@
           <t>8</t>
         </is>
       </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>1, 10A, 10B, 11, 12, 13, 14A, 14B, 2, 3, 4, 5, 6, 7, 8A, 8B, 9</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -3385,6 +3470,11 @@
           <t>80</t>
         </is>
       </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 20A, 20B, 20C, 21, 22, 2A, 2B, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -3392,6 +3482,11 @@
           <t>81</t>
         </is>
       </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6, 7</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -3399,6 +3494,11 @@
           <t>82</t>
         </is>
       </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>1, 10, 11A, 11B, 12, 13, 14, 15, 2, 3A, 3B, 3C, 4, 5A, 5B, 5C, 5D, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -3406,6 +3506,11 @@
           <t>83</t>
         </is>
       </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>1, 10, 11A, 11B, 11C1, 11C2, 12A, 12B, 13A, 13B, 14, 15, 16, 17, 18A, 18B, 19, 2, 20A, 20B, 21, 3A, 3B, 3C, 4, 5A, 5B, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -3413,6 +3518,11 @@
           <t>84</t>
         </is>
       </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>10A, 10B, 11, 12, 13, 14, 15, 16, 17, 18, 19, 1A, 1B, 2, 20, 21, 22, 23, 24, 25, 26, 27, 28, 29, 3, 30, 31, 32A, 32B, 33, 34, 35, 36, 4, 5, 6, 7, 8, 9A, 9B</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -3420,6 +3530,11 @@
           <t>85</t>
         </is>
       </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 13, 14, 15, 16, 17, 18A, 18B, 18C, 19, 1A, 1B, 2, 3A1, 3A2, 3B, 4, 5A, 5B, 5C, 6A, 6B, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -3427,6 +3542,11 @@
           <t>86</t>
         </is>
       </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -3434,6 +3554,11 @@
           <t>87</t>
         </is>
       </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -3441,6 +3566,11 @@
           <t>88</t>
         </is>
       </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 1D, 1E, 1F, 1G, 1H, 1I, 2, 3A, 3B, 3C, 3D, 4, 5A, 5B, 5C1, 5C2, 5D</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -3448,6 +3578,11 @@
           <t>89</t>
         </is>
       </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>1, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -3455,6 +3590,11 @@
           <t>9</t>
         </is>
       </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -3462,6 +3602,11 @@
           <t>90</t>
         </is>
       </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -3469,6 +3614,11 @@
           <t>91</t>
         </is>
       </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -3476,6 +3626,11 @@
           <t>92</t>
         </is>
       </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4A, 4B, 4C, 5, 6, 7, 8</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -3483,6 +3638,11 @@
           <t>93</t>
         </is>
       </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B, 3A1, 3A2, 3A3, 3B1, 3B2, 4A, 4B</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -3490,6 +3650,11 @@
           <t>94</t>
         </is>
       </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>1, 2, 3A, 3B, 3C, 3D, 4</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -3497,6 +3662,11 @@
           <t>95</t>
         </is>
       </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -3504,6 +3674,11 @@
           <t>96</t>
         </is>
       </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16A, 16B, 17, 18, 19A, 19B, 2, 20, 21A, 21B1, 21B2, 22, 23, 24A, 24B, 24C, 25, 26, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -3511,6 +3686,11 @@
           <t>97</t>
         </is>
       </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 2, 3, 4A, 4B, 5, 6A, 6B, 6C, 6D, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -3518,11 +3698,21 @@
           <t>98</t>
         </is>
       </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 2, 3, 4A, 4B, 5A, 5B, 6, 7A, 7B, 8A, 8B, 9</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
           <t>99</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15A, 15B, 16, 2A, 2B, 3, 4, 5, 6, 7, 8, 9</t>
         </is>
       </c>
     </row>

--- a/out/Village_map_of_Tiruvallur_Gummidipoondi_Manellore_13.455683_80.019989.xlsx
+++ b/out/Village_map_of_Tiruvallur_Gummidipoondi_Manellore_13.455683_80.019989.xlsx
@@ -1406,6 +1406,11 @@
           <t>172</t>
         </is>
       </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16A, 16B, 16C, 16D, 16E, 16F, 16G, 16H, 16I, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -1413,6 +1418,11 @@
           <t>173</t>
         </is>
       </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2A, 2B, 3, 4A, 4B, 5A, 5B, 6, 7A, 7B, 8A, 8B1, 8B2, 8C</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -1420,6 +1430,11 @@
           <t>174</t>
         </is>
       </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>1, 2A1, 2A2, 2A3, 2A4, 2B</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -1427,6 +1442,11 @@
           <t>175</t>
         </is>
       </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>1, 10, 11A, 11B, 11C1, 11C2, 11C3, 11C4, 12, 2A, 2B1, 2B2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -1434,6 +1454,11 @@
           <t>176</t>
         </is>
       </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12A, 12B, 13, 14, 15A, 15B, 15C, 16, 17, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -1441,6 +1466,11 @@
           <t>177</t>
         </is>
       </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>10A, 10B, 10C, 10D, 10E, 11, 12, 13, 1A, 1B, 1C, 1D, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -1448,6 +1478,11 @@
           <t>178</t>
         </is>
       </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 2, 3, 4, 5, 6, 7A, 7B, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -1455,6 +1490,11 @@
           <t>179</t>
         </is>
       </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>1, 10, 11A, 11B, 12, 2, 3, 4, 5, 6, 7A, 7B, 8A, 8B, 9</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -1462,6 +1502,11 @@
           <t>18</t>
         </is>
       </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13A, 13B, 2, 3, 4, 5A, 5B, 5C, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -1469,6 +1514,11 @@
           <t>180</t>
         </is>
       </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 2, 3, 4, 5, 6, 7A, 7B, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -1476,6 +1526,11 @@
           <t>181</t>
         </is>
       </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18A, 18B, 2, 3, 4, 5, 6, 7, 8, 9A, 9B</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -1483,6 +1538,11 @@
           <t>182</t>
         </is>
       </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17A, 17B, 17C, 18, 19, 2, 20, 21, 22, 23, 3, 4, 5, 6, 7A1, 7A2, 7B, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -1490,6 +1550,11 @@
           <t>183</t>
         </is>
       </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6A1, 6A2, 6B1, 6B2, 6B3, 6C1, 6C2, 6C3, 6D1, 6D2, 6D3, 6D4, 7A, 7B, 8A, 8B, 8C, 9A, 9B</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -1497,6 +1562,11 @@
           <t>184</t>
         </is>
       </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 2, 3, 4, 5A, 5B, 6, 7A, 7B, 7C, 7D, 7E, 7F1, 7F2, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -1504,6 +1574,11 @@
           <t>185</t>
         </is>
       </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14A1, 14A2, 14B, 15, 16A, 16B, 17, 18, 19, 20, 2A, 2B, 2C, 2D, 2E, 2F, 2G, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -1511,6 +1586,11 @@
           <t>186</t>
         </is>
       </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -1518,6 +1598,11 @@
           <t>187</t>
         </is>
       </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -1525,6 +1610,11 @@
           <t>188</t>
         </is>
       </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -1532,6 +1622,11 @@
           <t>189</t>
         </is>
       </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 13, 14, 15, 16, 17, 18, 1A, 1B, 1C, 1D, 1E, 1F, 2, 3, 4, 5, 6, 7A, 7B, 7C, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -1539,6 +1634,11 @@
           <t>19</t>
         </is>
       </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -1546,6 +1646,11 @@
           <t>190</t>
         </is>
       </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 20, 21, 22, 23, 2A, 2B, 2C, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -1553,6 +1658,11 @@
           <t>191</t>
         </is>
       </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12A, 12B, 12C, 13, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -1560,6 +1670,11 @@
           <t>192</t>
         </is>
       </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 2, 3, 4, 5, 6, 7, 8, 9A, 9B</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -1567,6 +1682,11 @@
           <t>193</t>
         </is>
       </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13A, 13B, 14, 15, 16, 17, 18, 19A, 19B, 2, 20, 21, 22, 23, 24, 25, 26, 3, 4, 5, 6A, 6B, 6C, 6D, 6E, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -1574,6 +1694,11 @@
           <t>194</t>
         </is>
       </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 20, 21, 22, 23, 24, 25, 26, 27, 28, 29, 2A, 2B, 30, 31, 32, 33, 34, 35, 36, 3A, 3B, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -1581,6 +1706,11 @@
           <t>195</t>
         </is>
       </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>1, 10, 11A, 11B, 11C, 11D, 11E, 12, 13A, 13B, 14, 15, 16, 17, 18, 19, 2, 20, 21, 22, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -1588,6 +1718,11 @@
           <t>196</t>
         </is>
       </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>1, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -1595,6 +1730,11 @@
           <t>197</t>
         </is>
       </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>1, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -1602,6 +1742,11 @@
           <t>198</t>
         </is>
       </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -1609,6 +1754,11 @@
           <t>199</t>
         </is>
       </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -1616,6 +1766,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6A, 6B, 6C, 7, 8A, 8B, 8C</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -1623,6 +1778,11 @@
           <t>20</t>
         </is>
       </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -1630,6 +1790,11 @@
           <t>200</t>
         </is>
       </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -1637,6 +1802,11 @@
           <t>201</t>
         </is>
       </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -1644,6 +1814,11 @@
           <t>202</t>
         </is>
       </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -1651,6 +1826,11 @@
           <t>203</t>
         </is>
       </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>1, 2A1, 2A2, 2A3, 2A4, 2A5, 2A6, 2A7, 2B, 3, 4</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -1658,6 +1838,11 @@
           <t>204</t>
         </is>
       </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -1665,6 +1850,11 @@
           <t>205</t>
         </is>
       </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -1672,6 +1862,11 @@
           <t>206</t>
         </is>
       </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -1679,6 +1874,11 @@
           <t>207</t>
         </is>
       </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -1686,6 +1886,11 @@
           <t>208</t>
         </is>
       </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -1693,6 +1898,11 @@
           <t>209</t>
         </is>
       </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -1700,6 +1910,11 @@
           <t>21</t>
         </is>
       </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -1707,6 +1922,11 @@
           <t>210</t>
         </is>
       </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -1714,6 +1934,11 @@
           <t>211</t>
         </is>
       </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -1721,6 +1946,11 @@
           <t>212</t>
         </is>
       </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -1728,6 +1958,11 @@
           <t>213</t>
         </is>
       </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -1735,6 +1970,11 @@
           <t>214</t>
         </is>
       </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -1742,6 +1982,11 @@
           <t>215</t>
         </is>
       </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -1749,6 +1994,11 @@
           <t>216</t>
         </is>
       </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -1756,6 +2006,11 @@
           <t>217</t>
         </is>
       </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -1763,6 +2018,11 @@
           <t>218</t>
         </is>
       </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -1770,6 +2030,11 @@
           <t>219</t>
         </is>
       </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -1777,6 +2042,11 @@
           <t>22</t>
         </is>
       </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 1D1, 1D2, 1E1, 1E2, 1F, 2A, 2B, 3A, 3B, 4</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -1784,6 +2054,11 @@
           <t>220</t>
         </is>
       </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -1791,6 +2066,11 @@
           <t>221</t>
         </is>
       </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2A, 3, 4, 5, 6</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -1798,6 +2078,11 @@
           <t>222</t>
         </is>
       </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 2A, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -1805,6 +2090,11 @@
           <t>223</t>
         </is>
       </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -1812,6 +2102,11 @@
           <t>224</t>
         </is>
       </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -1819,6 +2114,11 @@
           <t>225</t>
         </is>
       </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>1A, 2</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -1826,6 +2126,11 @@
           <t>226</t>
         </is>
       </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -1833,6 +2138,11 @@
           <t>227</t>
         </is>
       </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -1840,6 +2150,11 @@
           <t>228</t>
         </is>
       </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -1847,6 +2162,11 @@
           <t>229</t>
         </is>
       </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -1854,6 +2174,11 @@
           <t>23</t>
         </is>
       </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>10, 1A, 1B, 1C, 1D, 1E, 1F, 2A, 2B, 3A, 3B, 3C, 3D, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -1861,6 +2186,11 @@
           <t>230</t>
         </is>
       </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -1868,6 +2198,11 @@
           <t>231</t>
         </is>
       </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -1875,6 +2210,11 @@
           <t>232</t>
         </is>
       </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -1882,6 +2222,11 @@
           <t>233</t>
         </is>
       </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>1, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -1889,6 +2234,11 @@
           <t>234</t>
         </is>
       </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -1896,6 +2246,11 @@
           <t>235</t>
         </is>
       </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>1, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -1903,6 +2258,11 @@
           <t>236</t>
         </is>
       </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -1910,6 +2270,11 @@
           <t>237</t>
         </is>
       </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -1917,6 +2282,11 @@
           <t>238</t>
         </is>
       </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -1924,6 +2294,11 @@
           <t>239</t>
         </is>
       </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -1931,6 +2306,11 @@
           <t>24</t>
         </is>
       </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>1, 10A, 10B, 11, 12A, 12B, 13, 14, 2, 3, 4, 5, 6A, 6B, 7A, 7B, 7C, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -1938,6 +2318,11 @@
           <t>240</t>
         </is>
       </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -1945,6 +2330,11 @@
           <t>241</t>
         </is>
       </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -1952,6 +2342,11 @@
           <t>242</t>
         </is>
       </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -1959,11 +2354,21 @@
           <t>243</t>
         </is>
       </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
           <t>244</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>

--- a/out/Village_map_of_Tiruvallur_Gummidipoondi_Manellore_13.455683_80.019989.xlsx
+++ b/out/Village_map_of_Tiruvallur_Gummidipoondi_Manellore_13.455683_80.019989.xlsx
@@ -2378,6 +2378,11 @@
           <t>245</t>
         </is>
       </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -2385,6 +2390,11 @@
           <t>246</t>
         </is>
       </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -2392,6 +2402,11 @@
           <t>247</t>
         </is>
       </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -2399,6 +2414,11 @@
           <t>248</t>
         </is>
       </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -2406,6 +2426,11 @@
           <t>249</t>
         </is>
       </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -2413,6 +2438,11 @@
           <t>25</t>
         </is>
       </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12A, 12B, 12C, 12D, 13, 14, 15, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -2420,6 +2450,11 @@
           <t>250</t>
         </is>
       </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -2427,6 +2462,11 @@
           <t>251</t>
         </is>
       </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -2434,6 +2474,11 @@
           <t>252</t>
         </is>
       </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -2441,6 +2486,11 @@
           <t>253</t>
         </is>
       </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -2448,6 +2498,11 @@
           <t>254</t>
         </is>
       </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6, 7</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -2455,6 +2510,11 @@
           <t>255</t>
         </is>
       </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -2462,6 +2522,11 @@
           <t>256</t>
         </is>
       </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>1B, 2, 3, 4, 5</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -2469,6 +2534,11 @@
           <t>257</t>
         </is>
       </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -2476,6 +2546,11 @@
           <t>258</t>
         </is>
       </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -2483,6 +2558,11 @@
           <t>259</t>
         </is>
       </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 2, 3, 4, 5, 6</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -2490,6 +2570,11 @@
           <t>26</t>
         </is>
       </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>10A, 10B, 10C, 10D, 10E, 10F, 10G, 10H, 10I, 11A, 11B1, 11B2, 11C, 11D1, 11D2, 11E, 11F, 1A, 1B, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -2497,6 +2582,11 @@
           <t>260</t>
         </is>
       </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -2504,6 +2594,11 @@
           <t>261</t>
         </is>
       </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5A, 5B</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -2511,6 +2606,11 @@
           <t>262</t>
         </is>
       </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>1, 2, 3A, 3B, 3C, 3D, 4A</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -2518,6 +2618,11 @@
           <t>263</t>
         </is>
       </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>1A1, 1A2, 1B1A1, 1B1A2, 1B1B, 1B2A1, 1B2A2, 1B2B, 2, 3A, 3B, 3C, 4A1, 4A2, 4B, 5</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -2525,6 +2630,11 @@
           <t>264</t>
         </is>
       </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -2532,6 +2642,11 @@
           <t>265</t>
         </is>
       </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -2539,6 +2654,11 @@
           <t>266</t>
         </is>
       </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>1A, 2A, 2B, 3, 4A, 4B1, 4B2, 5A, 5B, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -2546,6 +2666,11 @@
           <t>267</t>
         </is>
       </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -2553,6 +2678,11 @@
           <t>268</t>
         </is>
       </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -2560,6 +2690,11 @@
           <t>269</t>
         </is>
       </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -2567,6 +2702,11 @@
           <t>27</t>
         </is>
       </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>10, 11A1, 11A2, 11A3, 11A4, 11A5, 11B, 1A, 1B, 2A, 2B, 2C, 2D, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -2574,6 +2714,11 @@
           <t>270</t>
         </is>
       </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B, 3A, 3B</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -2581,6 +2726,11 @@
           <t>271</t>
         </is>
       </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -2588,6 +2738,11 @@
           <t>272</t>
         </is>
       </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -2595,6 +2750,11 @@
           <t>273</t>
         </is>
       </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -2602,6 +2762,11 @@
           <t>274</t>
         </is>
       </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -2609,6 +2774,11 @@
           <t>28</t>
         </is>
       </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 1D, 2, 3A1, 3A2, 3B, 3C1, 3C2, 4, 5, 6, 7, 8</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -2616,6 +2786,11 @@
           <t>29</t>
         </is>
       </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>1, 2A1, 2A2, 2A3, 2A4, 2B, 2C, 2D, 2E, 3</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -2623,6 +2798,11 @@
           <t>3</t>
         </is>
       </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>1, 2, 3A, 3B, 4</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -2630,6 +2810,11 @@
           <t>30</t>
         </is>
       </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5A, 5B</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -2637,6 +2822,11 @@
           <t>31</t>
         </is>
       </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>1A1, 1A2, 1B, 2A1, 2A2, 2A3, 2B, 3A1, 3A2, 3B, 4, 5, 6, 7A, 7B, 7C, 7D1, 7D2, 7D3</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -2644,6 +2834,11 @@
           <t>32</t>
         </is>
       </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5A, 5B, 5C, 5D, 5E, 6</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -2651,6 +2846,11 @@
           <t>33</t>
         </is>
       </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -2658,6 +2858,11 @@
           <t>34</t>
         </is>
       </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -2665,6 +2870,11 @@
           <t>35</t>
         </is>
       </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>1, 2, 3A, 3B, 3C1, 3C2, 3C3, 3C4, 3C5</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -2672,6 +2882,11 @@
           <t>36</t>
         </is>
       </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -2679,6 +2894,11 @@
           <t>37</t>
         </is>
       </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -2686,6 +2906,11 @@
           <t>38</t>
         </is>
       </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -2693,11 +2918,21 @@
           <t>39</t>
         </is>
       </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
           <t>4</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B</t>
         </is>
       </c>
     </row>

--- a/out/Village_map_of_Tiruvallur_Gummidipoondi_Manellore_13.455683_80.019989.xlsx
+++ b/out/Village_map_of_Tiruvallur_Gummidipoondi_Manellore_13.455683_80.019989.xlsx
@@ -2942,6 +2942,11 @@
           <t>40</t>
         </is>
       </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -2949,6 +2954,11 @@
           <t>41</t>
         </is>
       </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -2956,6 +2966,11 @@
           <t>42</t>
         </is>
       </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -2963,6 +2978,11 @@
           <t>43</t>
         </is>
       </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -2970,6 +2990,11 @@
           <t>44</t>
         </is>
       </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 2, 22, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -2977,6 +3002,11 @@
           <t>45</t>
         </is>
       </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>1, 2, 3A, 3B, 3C, 3D, 3E, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -2984,6 +3014,11 @@
           <t>46</t>
         </is>
       </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 20, 21, 22, 23, 24, 25, 26, 2A, 2B, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -2991,6 +3026,11 @@
           <t>47</t>
         </is>
       </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>1, 10, 11A, 11B, 11C, 11D, 11E, 11F, 11G, 12, 13, 14, 15, 16, 17, 18, 19, 2, 20, 21, 22, 3A, 3B, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -2998,6 +3038,11 @@
           <t>48</t>
         </is>
       </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 1A, 1B, 1C, 1D, 2, 20, 21, 22, 23, 24, 25, 26, 27, 28, 29, 3, 30, 31, 32, 33, 34, 35, 36, 37, 38, 39, 4, 40, 41, 42, 43, 44, 45, 46, 47A, 47B, 47C, 47D, 47E, 47F, 48, 49, 5, 50, 51, 52, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -3005,6 +3050,11 @@
           <t>49</t>
         </is>
       </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>10, 11, 12A, 13A, 13B, 14A, 14B, 15, 16A, 16B, 17, 18, 19A, 19B, 1A, 2, 20A, 20B, 21A, 21B, 21C, 22A, 22B, 23A, 23B, 24, 25, 26, 3, 37, 38, 39, 4, 40, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -3012,6 +3062,11 @@
           <t>5</t>
         </is>
       </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2A, 2B, 2C, 3A, 3B, 3C</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -3019,6 +3074,11 @@
           <t>50</t>
         </is>
       </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12A, 12B, 13, 14, 15, 16, 17, 18, 19, 2, 20A, 20B, 20C, 21, 22A, 22B, 23, 24, 25, 26, 27, 28, 29, 3, 30, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -3026,6 +3086,11 @@
           <t>51</t>
         </is>
       </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>1, 10, 11A, 11B, 11C, 11D, 11E, 11F, 12, 13, 14, 15A, 15B, 16A, 16B, 16C, 17, 18, 19, 2, 20, 21, 22, 23, 24, 25A, 25B, 26, 27, 28, 29, 3, 30, 4, 5, 6A, 6B, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -3033,6 +3098,11 @@
           <t>52</t>
         </is>
       </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -3040,6 +3110,11 @@
           <t>53</t>
         </is>
       </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -3047,6 +3122,11 @@
           <t>54</t>
         </is>
       </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -3054,6 +3134,11 @@
           <t>55</t>
         </is>
       </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -3061,6 +3146,11 @@
           <t>56</t>
         </is>
       </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -3068,6 +3158,11 @@
           <t>57</t>
         </is>
       </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -3075,6 +3170,11 @@
           <t>58</t>
         </is>
       </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -3082,6 +3182,11 @@
           <t>59</t>
         </is>
       </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -3089,6 +3194,11 @@
           <t>6</t>
         </is>
       </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12A, 12B, 12C, 13A, 13B, 13C, 2, 3, 4A, 4B, 4C, 5A, 5B, 5C, 6, 7A, 7B, 7C, 8, 9A, 9B</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -3096,6 +3206,11 @@
           <t>60</t>
         </is>
       </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -3103,6 +3218,11 @@
           <t>61</t>
         </is>
       </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13A1, 13A2, 13B, 14, 15, 2, 3, 4, 5, 6, 7, 8A, 8B, 9</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -3110,6 +3230,11 @@
           <t>62</t>
         </is>
       </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -3117,6 +3242,11 @@
           <t>63</t>
         </is>
       </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13A, 13B, 14A, 14B, 15, 16, 17, 18, 19, 2, 20, 21, 22, 23, 24, 25, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -3124,6 +3254,11 @@
           <t>64</t>
         </is>
       </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -3131,6 +3266,11 @@
           <t>65</t>
         </is>
       </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 1A, 1B, 2, 20, 21, 22, 23, 24, 25, 26, 27, 28, 29, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -3138,6 +3278,11 @@
           <t>66</t>
         </is>
       </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -3145,6 +3290,11 @@
           <t>67</t>
         </is>
       </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -3152,6 +3302,11 @@
           <t>68</t>
         </is>
       </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -3159,6 +3314,11 @@
           <t>69</t>
         </is>
       </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 1A1A, 1A1B, 1A2, 1B, 1C, 1D, 2, 20, 21, 22, 23, 24, 25, 3A1, 3A2, 3A3, 3A4, 3B, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -3166,6 +3326,11 @@
           <t>7</t>
         </is>
       </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 2A, 2B, 3, 4, 5, 6</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -3173,6 +3338,11 @@
           <t>70</t>
         </is>
       </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -3180,6 +3350,11 @@
           <t>71</t>
         </is>
       </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 2, 20, 21, 22, 23, 24, 25, 26, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -3187,6 +3362,11 @@
           <t>72</t>
         </is>
       </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -3194,6 +3374,11 @@
           <t>73</t>
         </is>
       </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 1D, 1E, 2A, 2B, 2C, 2D, 3, 4A, 4B, 5A1, 5A2, 5B, 5C</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -3201,6 +3386,11 @@
           <t>74</t>
         </is>
       </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -3208,6 +3398,11 @@
           <t>75</t>
         </is>
       </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -3215,6 +3410,11 @@
           <t>76</t>
         </is>
       </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -3222,6 +3422,11 @@
           <t>77</t>
         </is>
       </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -3229,6 +3434,11 @@
           <t>78</t>
         </is>
       </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>1, 10, 2A1, 2A2, 2B, 2C, 3, 4A, 4B, 5, 6A, 6B, 7A, 7B, 7C, 7D, 7E, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -3236,6 +3446,11 @@
           <t>79</t>
         </is>
       </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 1A, 1B, 2, 3A, 3B, 3C, 3D, 4, 5, 6, 7, 8, 9A, 9B</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -3243,6 +3458,11 @@
           <t>8</t>
         </is>
       </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>1, 10A, 10B, 11, 12, 13, 14A, 14B, 2, 3, 4, 5, 6, 7, 8A, 8B, 9</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -3250,6 +3470,11 @@
           <t>80</t>
         </is>
       </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 20A, 20B, 20C, 21, 22, 2A, 2B, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -3257,6 +3482,11 @@
           <t>81</t>
         </is>
       </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6, 7</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -3264,6 +3494,11 @@
           <t>82</t>
         </is>
       </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>1, 10, 11A, 11B, 12, 13, 14, 15, 2, 3A, 3B, 3C, 4, 5A, 5B, 5C, 5D, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -3271,6 +3506,11 @@
           <t>83</t>
         </is>
       </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>1, 10, 11A, 11B, 11C1, 11C2, 12A, 12B, 13A, 13B, 14, 15, 16, 17, 18A, 18B, 19, 2, 20A, 20B, 21, 3A, 3B, 3C, 4, 5A, 5B, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -3278,6 +3518,11 @@
           <t>84</t>
         </is>
       </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>10A, 10B, 11, 12, 13, 14, 15, 16, 17, 18, 19, 1A, 1B, 2, 20, 21, 22, 23, 24, 25, 26, 27, 28, 29, 3, 30, 31, 32A, 32B, 33, 34, 35, 36, 4, 5, 6, 7, 8, 9A, 9B</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -3285,6 +3530,11 @@
           <t>85</t>
         </is>
       </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 13, 14, 15, 16, 17, 18A, 18B, 18C, 19, 1A, 1B, 2, 3A1, 3A2, 3B, 4, 5A, 5B, 5C, 6A, 6B, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -3292,6 +3542,11 @@
           <t>86</t>
         </is>
       </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -3299,6 +3554,11 @@
           <t>87</t>
         </is>
       </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -3306,6 +3566,11 @@
           <t>88</t>
         </is>
       </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 1D, 1E, 1F, 1G, 1H, 1I, 2, 3A, 3B, 3C, 3D, 4, 5A, 5B, 5C1, 5C2, 5D</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -3313,6 +3578,11 @@
           <t>89</t>
         </is>
       </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>1, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -3320,6 +3590,11 @@
           <t>9</t>
         </is>
       </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -3327,6 +3602,11 @@
           <t>90</t>
         </is>
       </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -3334,6 +3614,11 @@
           <t>91</t>
         </is>
       </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -3341,6 +3626,11 @@
           <t>92</t>
         </is>
       </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4A, 4B, 4C, 5, 6, 7, 8</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -3348,6 +3638,11 @@
           <t>93</t>
         </is>
       </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B, 3A1, 3A2, 3A3, 3B1, 3B2, 4A, 4B</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -3355,6 +3650,11 @@
           <t>94</t>
         </is>
       </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>1, 2, 3A, 3B, 3C, 3D, 4</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -3362,6 +3662,11 @@
           <t>95</t>
         </is>
       </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -3369,6 +3674,11 @@
           <t>96</t>
         </is>
       </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16A, 16B, 17, 18, 19A, 19B, 2, 20, 21A, 21B1, 21B2, 22, 23, 24A, 24B, 24C, 25, 26, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -3376,6 +3686,11 @@
           <t>97</t>
         </is>
       </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 2, 3, 4A, 4B, 5, 6A, 6B, 6C, 6D, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -3383,11 +3698,21 @@
           <t>98</t>
         </is>
       </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 2, 3, 4A, 4B, 5A, 5B, 6, 7A, 7B, 8A, 8B, 9</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
           <t>99</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15A, 15B, 16, 2A, 2B, 3, 4, 5, 6, 7, 8, 9</t>
         </is>
       </c>
     </row>
